--- a/Result/profitability/3483.xlsx
+++ b/Result/profitability/3483.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2525</v>
+        <v>1.1525</v>
       </c>
       <c r="N2" t="n">
-        <v>20.5525</v>
+        <v>20.125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.95</v>
       </c>
       <c r="M3" t="n">
-        <v>1.20625</v>
+        <v>0.9325</v>
       </c>
       <c r="N3" t="n">
-        <v>21.3675</v>
+        <v>20.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.22</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.0775</v>
       </c>
       <c r="N4" t="n">
-        <v>21.51125</v>
+        <v>21.3675</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.34</v>
       </c>
       <c r="M5" t="n">
-        <v>1.055</v>
+        <v>0.9387500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>22.17875</v>
+        <v>21.43125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>1.045</v>
+        <v>0.9075000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>22.92875</v>
+        <v>22.42375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02875</v>
+        <v>1.0175</v>
       </c>
       <c r="N7" t="n">
-        <v>23.8425</v>
+        <v>23.59</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2025</v>
+        <v>1.24625</v>
       </c>
       <c r="N8" t="n">
-        <v>24.775</v>
+        <v>24.63875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.45</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7125</v>
+        <v>0.7124999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>20.87375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3483</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2225</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1869</v>
+      </c>
+      <c r="E75" t="n">
+        <v>356</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>71</v>
+      </c>
+      <c r="J75" t="n">
+        <v>66</v>
+      </c>
+      <c r="K75" t="n">
+        <v>51</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.058823529411764</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.089999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06381733021077274</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.9299999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6413793103448275</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.979999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.272189349112426</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
